--- a/example.xlsx
+++ b/example.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="127">
   <si>
     <t>con_ID</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>CHATSENDTIMEORI</t>
+  </si>
+  <si>
+    <t>TRADERNAME</t>
+  </si>
+  <si>
+    <t>INTERLOCUTOR</t>
   </si>
   <si>
     <t>is_start</t>
@@ -55,6 +61,9 @@
   </si>
   <si>
     <t>2026-04-29 08:47:54.000</t>
+  </si>
+  <si>
+    <t>刘安琪</t>
   </si>
   <si>
     <t>{
@@ -116,9 +125,6 @@
     }
   ]
 }</t>
-  </si>
-  <si>
-    <t>刘安琪</t>
   </si>
   <si>
     <t>1000我得比较贵</t>
@@ -2081,18 +2087,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="26.6666666666667" customWidth="1"/>
     <col min="3" max="3" width="68.1481481481482" customWidth="1"/>
-    <col min="4" max="4" width="15.962962962963" customWidth="1"/>
-    <col min="5" max="5" width="17.5185185185185" customWidth="1"/>
-    <col min="6" max="6" width="45.7962962962963" customWidth="1"/>
+    <col min="4" max="5" width="15.962962962963" customWidth="1"/>
+    <col min="6" max="6" width="18.462962962963" customWidth="1"/>
+    <col min="7" max="7" width="17.5185185185185" customWidth="1"/>
+    <col min="8" max="8" width="45.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:6">
+    <row r="1" ht="28.8" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2111,945 +2118,1233 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="273.6" customHeight="1" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="273.6" customHeight="1" spans="1:8">
       <c r="A2" s="3">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="b">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="273.6" customHeight="1" spans="1:6">
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="273.6" customHeight="1" spans="1:8">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" ht="374.4" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="374.4" customHeight="1" spans="1:8">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="374.4" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="374.4" customHeight="1" spans="1:8">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="374.4" customHeight="1" spans="1:6">
+    </row>
+    <row r="6" ht="374.4" customHeight="1" spans="1:8">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="374.4" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="374.4" customHeight="1" spans="1:8">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="374.4" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="374.4" customHeight="1" spans="1:8">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" ht="374.4" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="374.4" customHeight="1" spans="1:8">
       <c r="A9" s="3">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="408" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="408" customHeight="1" spans="1:8">
       <c r="A10" s="3">
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3" t="b">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" customHeight="1" spans="1:6">
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customHeight="1" spans="1:8">
       <c r="A11" s="3">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="409.5" customHeight="1" spans="1:8">
       <c r="A12" s="3">
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="409.5" customHeight="1" spans="1:8">
       <c r="A13" s="3">
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" ht="409.5" customHeight="1" spans="1:8">
       <c r="A14" s="3">
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="409.5" customHeight="1" spans="1:8">
       <c r="A15" s="3">
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" ht="409.5" customHeight="1" spans="1:8">
       <c r="A16" s="3">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" ht="409.5" customHeight="1" spans="1:8">
       <c r="A17" s="3">
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" ht="409.5" customHeight="1" spans="1:8">
       <c r="A18" s="3">
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" ht="409.5" customHeight="1" spans="1:6">
+    </row>
+    <row r="19" ht="409.5" customHeight="1" spans="1:8">
       <c r="A19" s="3">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="409.5" customHeight="1" spans="1:8">
       <c r="A20" s="3">
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="409.5" customHeight="1" spans="1:8">
       <c r="A21" s="3">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="409.5" customHeight="1" spans="1:8">
       <c r="A22" s="3">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="409.5" customHeight="1" spans="1:8">
       <c r="A23" s="3">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" ht="409.5" customHeight="1" spans="1:8">
       <c r="A24" s="3">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" ht="409.5" customHeight="1" spans="1:8">
       <c r="A25" s="3">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" ht="409.5" customHeight="1" spans="1:6">
+    </row>
+    <row r="26" ht="409.5" customHeight="1" spans="1:8">
       <c r="A26" s="3">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" ht="409.5" customHeight="1" spans="1:8">
       <c r="A27" s="3">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="3" t="b">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" ht="409.5" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" ht="409.5" customHeight="1" spans="1:8">
       <c r="A28" s="3">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" ht="172.8" customHeight="1" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" ht="172.8" customHeight="1" spans="1:8">
       <c r="A29" s="3">
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="3" t="b">
+      <c r="G29" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" ht="172.8" customHeight="1" spans="1:6">
+      <c r="H29" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" ht="172.8" customHeight="1" spans="1:8">
       <c r="A30" s="3">
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" s="3" t="b">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" ht="172.8" customHeight="1" spans="1:6">
+        <v>77</v>
+      </c>
+      <c r="G30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" ht="172.8" customHeight="1" spans="1:8">
       <c r="A31" s="3">
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="3" t="b">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="172.8" customHeight="1" spans="1:6">
+        <v>77</v>
+      </c>
+      <c r="G31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="172.8" customHeight="1" spans="1:8">
       <c r="A32" s="4">
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" ht="172.8" customHeight="1" spans="1:6">
+    </row>
+    <row r="33" ht="172.8" customHeight="1" spans="1:8">
       <c r="A33" s="3">
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" ht="172.8" customHeight="1" spans="1:6">
+        <v>77</v>
+      </c>
+      <c r="G33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" ht="172.8" customHeight="1" spans="1:8">
       <c r="A34" s="3">
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="3" t="b">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" ht="172.8" customHeight="1" spans="1:6">
+        <v>77</v>
+      </c>
+      <c r="G34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" ht="172.8" customHeight="1" spans="1:8">
       <c r="A35" s="3">
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" ht="172.8" customHeight="1" spans="1:6">
+    </row>
+    <row r="36" ht="172.8" customHeight="1" spans="1:8">
       <c r="A36" s="3">
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="3" t="b">
+      <c r="G36" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" ht="172.8" customHeight="1" spans="1:6">
+      <c r="H36" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" ht="172.8" customHeight="1" spans="1:8">
       <c r="A37" s="3">
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="3" t="b">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" ht="374.4" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" ht="374.4" customHeight="1" spans="1:8">
       <c r="A38" s="3">
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="3" t="b">
+        <v>104</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" ht="374.4" customHeight="1" spans="1:6">
+      <c r="H38" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" ht="374.4" customHeight="1" spans="1:8">
       <c r="A39" s="3">
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="3" t="b">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" ht="374.4" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" ht="374.4" customHeight="1" spans="1:8">
       <c r="A40" s="3">
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="41" ht="374.4" customHeight="1" spans="1:6">
+    </row>
+    <row r="41" ht="374.4" customHeight="1" spans="1:8">
       <c r="A41" s="3">
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>0</v>
+        <v>112</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="42" ht="374.4" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" ht="374.4" customHeight="1" spans="1:8">
       <c r="A42" s="3">
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" ht="374.4" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" ht="374.4" customHeight="1" spans="1:8">
       <c r="A43" s="3">
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" ht="409.5" customHeight="1" spans="1:6">
+    </row>
+    <row r="44" ht="409.5" customHeight="1" spans="1:8">
       <c r="A44" s="3">
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" s="3" t="b">
+        <v>119</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" ht="409.5" customHeight="1" spans="1:6">
+      <c r="H44" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" ht="409.5" customHeight="1" spans="1:8">
       <c r="A45" s="3">
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" s="3" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" ht="409.5" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" customHeight="1" spans="1:8">
       <c r="A46" s="3">
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E46" s="3" t="b">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" ht="409.5" customHeight="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" customHeight="1" spans="1:8">
       <c r="A47" s="3">
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" ht="409.5" customHeight="1" spans="1:6">
+    </row>
+    <row r="48" ht="409.5" customHeight="1" spans="1:8">
       <c r="A48" s="3">
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" s="3" t="b">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>120</v>
+        <v>96</v>
+      </c>
+      <c r="G48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/example.xlsx
+++ b/example.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="128">
   <si>
     <t>con_ID</t>
   </si>
@@ -889,21 +889,21 @@
       "account": "圆融安享10号",
       "amount": "5550万",
       "term": "隔夜",
-      "price": "",
+      "price": "41",
       "intent": "价格议价期限调整"
     },
     {
       "account": "锦鸿1号",
       "amount": "15410万",
       "term": "隔夜",
-      "price": "",
+      "price": "41",
       "intent": "价格议价期限调整"
     },
     {
       "account": "锦鸿3号",
       "amount": "7820万",
       "term": "隔夜",
-      "price": "",
+      "price": "41",
       "intent": "价格议价期限调整"
     }
   ]
@@ -950,18 +950,6 @@
     <t>2026-04-29 08:37:19.000</t>
   </si>
   <si>
-    <t>圆融安享10号  5550万-汇享；锦鸿3号-汇盈</t>
-  </si>
-  <si>
-    <t>2026-04-29 08:38:24.000</t>
-  </si>
-  <si>
-    <t>你先都发汇享  一会有别的户我再帮你调</t>
-  </si>
-  <si>
-    <t>2026-04-29 08:39:13.000</t>
-  </si>
-  <si>
     <t>{
   "counterparty": "涂真",
   "trades": [
@@ -969,31 +957,71 @@
       "account": "圆融安享10号",
       "amount": "5550万",
       "term": "隔夜",
-      "price": "1.40",
-      "intent": "交易成交"
+      "price": "1.41",
+      "intent": "价格议价期限调整"
     },
     {
       "account": "锦鸿1号",
       "amount": "15410万",
       "term": "隔夜",
-      "price": "1.40",
-      "intent": "交易成交"
+      "price": "1.41",
+      "intent": "价格议价期限调整"
     },
     {
       "account": "锦鸿3号",
       "amount": "7820万",
       "term": "隔夜",
-      "price": "1.40",
-      "intent": "交易成交"
+      "price": "1.41",
+      "intent": "价格议价期限调整"
     }
   ]
 }</t>
   </si>
   <si>
+    <t>圆融安享10号  5550万-汇享；锦鸿3号-汇盈</t>
+  </si>
+  <si>
+    <t>2026-04-29 08:38:24.000</t>
+  </si>
+  <si>
+    <t>你先都发汇享  一会有别的户我再帮你调</t>
+  </si>
+  <si>
+    <t>2026-04-29 08:39:13.000</t>
+  </si>
+  <si>
     <t>好的</t>
   </si>
   <si>
     <t>2026-04-29 08:39:24.000</t>
+  </si>
+  <si>
+    <t>{
+  "counterparty": "涂真",
+  "trades": [
+    {
+      "account": "圆融安享10号",
+      "amount": "5550万",
+      "term": "隔夜",
+      "price": "1.41",
+      "intent": "交易成交"
+    },
+    {
+      "account": "锦鸿1号",
+      "amount": "15410万",
+      "term": "隔夜",
+      "price": "1.41",
+      "intent": "交易成交"
+    },
+    {
+      "account": "锦鸿3号",
+      "amount": "7820万",
+      "term": "隔夜",
+      "price": "1.41",
+      "intent": "交易成交"
+    }
+  ]
+}</t>
   </si>
   <si>
     <t>老板，还有6100W么？锦鸿2号借</t>
@@ -1009,28 +1037,28 @@
       "account": "圆融安享10号",
       "amount": "5550万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿1号",
       "amount": "15410万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿3号",
       "amount": "7820万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿2号",
       "amount": "6100w",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "价格议价期限调整"
     }
   ]
@@ -1048,28 +1076,28 @@
       "account": "圆融安享10号",
       "amount": "5550万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿1号",
       "amount": "15410万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿3号",
       "amount": "7820万",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     },
     {
       "account": "锦鸿2号",
       "amount": "6100w",
       "term": "隔夜",
-      "price": "1.40",
+      "price": "1.41",
       "intent": "交易成交"
     }
   ]
@@ -3136,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" ht="374.4" customHeight="1" spans="1:8">
@@ -3147,10 +3175,10 @@
         <v>96</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>11</v>
@@ -3162,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" ht="374.4" customHeight="1" spans="1:8">
@@ -3173,10 +3201,10 @@
         <v>11</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>11</v>
@@ -3188,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" ht="374.4" customHeight="1" spans="1:8">
@@ -3214,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" ht="409.5" customHeight="1" spans="1:8">
@@ -3225,10 +3253,10 @@
         <v>96</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>11</v>
@@ -3240,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" ht="409.5" customHeight="1" spans="1:8">
@@ -3254,7 +3282,7 @@
         <v>36</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>11</v>
@@ -3266,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" ht="409.5" customHeight="1" spans="1:8">
@@ -3280,7 +3308,7 @@
         <v>116</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>11</v>
@@ -3292,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" ht="409.5" customHeight="1" spans="1:8">
@@ -3303,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>11</v>
@@ -3318,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" ht="409.5" customHeight="1" spans="1:8">
@@ -3332,7 +3360,7 @@
         <v>116</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>11</v>
@@ -3344,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
